--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/pre LAM_HRM-2031-0400/Panel-28/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/pre LAM_HRM-2031-0400/Panel-28/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.85538</v>
+        <v>17.09442</v>
       </c>
       <c r="D2" t="n">
-        <v>17.01659</v>
+        <v>16.283</v>
       </c>
       <c r="E2" t="n">
-        <v>16.82922</v>
+        <v>16.63755</v>
       </c>
       <c r="F2" t="n">
-        <v>42.32098</v>
+        <v>43.45955</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04983</v>
+        <v>0.05106</v>
       </c>
       <c r="H2" t="n">
-        <v>1.85678</v>
+        <v>1.79885</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.9483</v>
+        <v>17.02126</v>
       </c>
       <c r="D3" t="n">
-        <v>16.5532</v>
+        <v>16.94089</v>
       </c>
       <c r="E3" t="n">
-        <v>17.04406</v>
+        <v>16.96295</v>
       </c>
       <c r="F3" t="n">
-        <v>42.92365</v>
+        <v>43.21753</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05197</v>
+        <v>0.05139</v>
       </c>
       <c r="H3" t="n">
-        <v>1.86643</v>
+        <v>1.80512</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.57613</v>
+        <v>16.95991</v>
       </c>
       <c r="D4" t="n">
-        <v>16.64476</v>
+        <v>16.57853</v>
       </c>
       <c r="E4" t="n">
-        <v>16.72323</v>
+        <v>16.8244</v>
       </c>
       <c r="F4" t="n">
-        <v>43.33417</v>
+        <v>43.31702</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05054</v>
+        <v>0.05131</v>
       </c>
       <c r="H4" t="n">
-        <v>1.84229</v>
+        <v>1.85764</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.89542</v>
+        <v>17.06784</v>
       </c>
       <c r="D6" t="n">
-        <v>15.79623</v>
+        <v>16.04433</v>
       </c>
       <c r="E6" t="n">
-        <v>16.67926</v>
+        <v>16.64406</v>
       </c>
       <c r="F6" t="n">
-        <v>21.72488</v>
+        <v>22.04565</v>
       </c>
       <c r="G6" t="n">
-        <v>33.68875</v>
+        <v>34.83434</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.13751</v>
+        <v>16.85906</v>
       </c>
       <c r="D7" t="n">
-        <v>15.982</v>
+        <v>16.47508</v>
       </c>
       <c r="E7" t="n">
-        <v>16.3565</v>
+        <v>16.50274</v>
       </c>
       <c r="F7" t="n">
-        <v>22.03342</v>
+        <v>21.9557</v>
       </c>
       <c r="G7" t="n">
-        <v>34.47081</v>
+        <v>34.08075</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.78859</v>
+        <v>16.59486</v>
       </c>
       <c r="D8" t="n">
-        <v>15.76284</v>
+        <v>16.09407</v>
       </c>
       <c r="E8" t="n">
-        <v>16.2831</v>
+        <v>16.2862</v>
       </c>
       <c r="F8" t="n">
-        <v>21.53859</v>
+        <v>22.30942</v>
       </c>
       <c r="G8" t="n">
-        <v>34.20257</v>
+        <v>34.35762</v>
       </c>
     </row>
   </sheetData>
